--- a/tame_output/ON/bt/strategyON_20230805.xlsx
+++ b/tame_output/ON/bt/strategyON_20230805.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,11 +610,11 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.0%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>83.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.86</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>71.1%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-5.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15.4%</t>
+          <t>14.0%</t>
         </is>
       </c>
     </row>
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -911,7 +911,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -977,12 +977,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>8.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-4.7%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.9%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.7%</t>
+          <t>456.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>11.9%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>108.7%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.39</t>
+          <t>3.37</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1130,12 +1130,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.5%</t>
+          <t>8.7%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>104.5%</t>
+          <t>104.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>18.8%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>3.6</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>141.4%</t>
+          <t>141.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,16 +1370,16 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.31</t>
+          <t>4.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-03</t>
+          <t>2023-08-04</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>135.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.5%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1679"/>
+  <dimension ref="A1:G1680"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40127,7 +40127,7 @@
         <v>45141</v>
       </c>
       <c r="B1679" t="n">
-        <v>2.877364893804671</v>
+        <v>2.877162372604197</v>
       </c>
       <c r="C1679" t="n">
         <v>3.008610455199692</v>
@@ -40143,6 +40143,29 @@
       </c>
       <c r="G1679" t="n">
         <v>4.299918581206174</v>
+      </c>
+    </row>
+    <row r="1680">
+      <c r="A1680" s="2" t="n">
+        <v>45142</v>
+      </c>
+      <c r="B1680" t="n">
+        <v>2.875118223650516</v>
+      </c>
+      <c r="C1680" t="n">
+        <v>2.995458941041095</v>
+      </c>
+      <c r="D1680" t="n">
+        <v>1.543334765370409</v>
+      </c>
+      <c r="E1680" t="n">
+        <v>3.612436422875513</v>
+      </c>
+      <c r="F1680" t="n">
+        <v>2.166526915224754</v>
+      </c>
+      <c r="G1680" t="n">
+        <v>4.295375090175949</v>
       </c>
     </row>
   </sheetData>
